--- a/etf_holdings/2026-09-09_00400A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-09_00400A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:49</t>
+          <t>2026-09-09 00:52:02</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:49</t>
+          <t>2026-09-09 00:52:02</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:49</t>
+          <t>2026-09-09 00:52:02</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:49</t>
+          <t>2026-09-09 00:52:02</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:49</t>
+          <t>2026-09-09 00:52:02</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:49</t>
+          <t>2026-09-09 00:52:02</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:49</t>
+          <t>2026-09-09 00:52:02</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:49</t>
+          <t>2026-09-09 00:52:02</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:49</t>
+          <t>2026-09-09 00:52:02</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:49</t>
+          <t>2026-09-09 00:52:02</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:49</t>
+          <t>2026-09-09 00:52:02</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:49</t>
+          <t>2026-09-09 00:52:02</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:49</t>
+          <t>2026-09-09 00:52:02</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:49</t>
+          <t>2026-09-09 00:52:02</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:49</t>
+          <t>2026-09-09 00:52:02</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:50</t>
+          <t>2026-09-09 00:52:03</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:50</t>
+          <t>2026-09-09 00:52:03</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:50</t>
+          <t>2026-09-09 00:52:03</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:50</t>
+          <t>2026-09-09 00:52:03</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:50</t>
+          <t>2026-09-09 00:52:03</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:50</t>
+          <t>2026-09-09 00:52:03</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:50</t>
+          <t>2026-09-09 00:52:03</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:50</t>
+          <t>2026-09-09 00:52:03</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:50</t>
+          <t>2026-09-09 00:52:03</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:50</t>
+          <t>2026-09-09 00:52:03</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:50</t>
+          <t>2026-09-09 00:52:03</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:50</t>
+          <t>2026-09-09 00:52:03</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:50</t>
+          <t>2026-09-09 00:52:03</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:50</t>
+          <t>2026-09-09 00:52:03</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:50</t>
+          <t>2026-09-09 00:52:03</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:51</t>
+          <t>2026-09-09 00:52:04</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:51</t>
+          <t>2026-09-09 00:52:04</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:51</t>
+          <t>2026-09-09 00:52:04</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:51</t>
+          <t>2026-09-09 00:52:04</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:51</t>
+          <t>2026-09-09 00:52:04</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:51</t>
+          <t>2026-09-09 00:52:04</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:51</t>
+          <t>2026-09-09 00:52:04</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:51</t>
+          <t>2026-09-09 00:52:04</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:51</t>
+          <t>2026-09-09 00:52:04</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:51</t>
+          <t>2026-09-09 00:52:04</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:51</t>
+          <t>2026-09-09 00:52:04</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:51</t>
+          <t>2026-09-09 00:52:04</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:51</t>
+          <t>2026-09-09 00:52:04</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:51</t>
+          <t>2026-09-09 00:52:04</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:51</t>
+          <t>2026-09-09 00:52:04</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">

--- a/etf_holdings/2026-09-09_00400A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-09_00400A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 00:52:02</t>
+          <t>2026-09-09 01:18:51</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09 00:52:02</t>
+          <t>2026-09-09 01:18:51</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09 00:52:02</t>
+          <t>2026-09-09 01:18:51</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-09 00:52:02</t>
+          <t>2026-09-09 01:18:51</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-09 00:52:02</t>
+          <t>2026-09-09 01:18:51</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-09 00:52:02</t>
+          <t>2026-09-09 01:18:51</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-09 00:52:02</t>
+          <t>2026-09-09 01:18:51</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-09 00:52:02</t>
+          <t>2026-09-09 01:18:51</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-09 00:52:02</t>
+          <t>2026-09-09 01:18:51</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-09 00:52:02</t>
+          <t>2026-09-09 01:18:51</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-09 00:52:02</t>
+          <t>2026-09-09 01:18:51</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-09 00:52:02</t>
+          <t>2026-09-09 01:18:51</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-09 00:52:02</t>
+          <t>2026-09-09 01:18:51</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-09 00:52:02</t>
+          <t>2026-09-09 01:18:51</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-09 00:52:02</t>
+          <t>2026-09-09 01:18:51</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-09 00:52:03</t>
+          <t>2026-09-09 01:18:52</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-09 00:52:03</t>
+          <t>2026-09-09 01:18:52</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-09 00:52:03</t>
+          <t>2026-09-09 01:18:52</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-09 00:52:03</t>
+          <t>2026-09-09 01:18:52</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-09 00:52:03</t>
+          <t>2026-09-09 01:18:52</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-09 00:52:03</t>
+          <t>2026-09-09 01:18:52</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-09 00:52:03</t>
+          <t>2026-09-09 01:18:52</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-09 00:52:03</t>
+          <t>2026-09-09 01:18:52</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-09 00:52:03</t>
+          <t>2026-09-09 01:18:52</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-09 00:52:03</t>
+          <t>2026-09-09 01:18:52</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-09 00:52:03</t>
+          <t>2026-09-09 01:18:52</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-09 00:52:03</t>
+          <t>2026-09-09 01:18:52</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-09 00:52:03</t>
+          <t>2026-09-09 01:18:52</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-09 00:52:03</t>
+          <t>2026-09-09 01:18:52</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-09 00:52:03</t>
+          <t>2026-09-09 01:18:52</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-09 00:52:04</t>
+          <t>2026-09-09 01:18:53</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-09 00:52:04</t>
+          <t>2026-09-09 01:18:53</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-09 00:52:04</t>
+          <t>2026-09-09 01:18:53</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-09 00:52:04</t>
+          <t>2026-09-09 01:18:53</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-09 00:52:04</t>
+          <t>2026-09-09 01:18:53</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-09 00:52:04</t>
+          <t>2026-09-09 01:18:53</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-09 00:52:04</t>
+          <t>2026-09-09 01:18:53</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-09 00:52:04</t>
+          <t>2026-09-09 01:18:53</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-09 00:52:04</t>
+          <t>2026-09-09 01:18:53</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-09 00:52:04</t>
+          <t>2026-09-09 01:18:53</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-09 00:52:04</t>
+          <t>2026-09-09 01:18:53</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-09 00:52:04</t>
+          <t>2026-09-09 01:18:53</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-09 00:52:04</t>
+          <t>2026-09-09 01:18:53</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-09 00:52:04</t>
+          <t>2026-09-09 01:18:53</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-09 00:52:04</t>
+          <t>2026-09-09 01:18:53</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">

--- a/etf_holdings/2026-09-09_00400A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-09_00400A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 01:18:51</t>
+          <t>2026-09-09 19:34:40</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+0.41%2470</t>
+          <t>-0.2%2465</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+0.41%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2470</v>
+        <v>2465</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8.91%1,034,000</t>
+          <t>8.90%1,034,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8.91%</t>
+          <t>8.90%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09 01:18:51</t>
+          <t>2026-09-09 19:34:40</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-1.05%4710</t>
+          <t>-1.8%4625</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-1.05%</t>
+          <t>-1.8%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4710</v>
+        <v>4625</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7.72%470,000</t>
+          <t>7.59%470,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>7.72%</t>
+          <t>7.59%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09 01:18:51</t>
+          <t>2026-09-09 19:34:40</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,25 +631,25 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-9.96%12520</t>
+          <t>-0.96%12400</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-9.96%</t>
+          <t>-0.96%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>12520</v>
+        <v>12400</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5.37%123,000</t>
+          <t>5.32%123,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5.37%</t>
+          <t>5.32%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.59%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-09 01:18:51</t>
+          <t>2026-09-09 19:34:40</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,25 +692,25 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+5.56%5795</t>
+          <t>-3.11%5615</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+5.56%</t>
+          <t>-3.11%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>5795</v>
+        <v>5615</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4.81%238,000</t>
+          <t>4.66%238,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>4.81%</t>
+          <t>4.66%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.25%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-09 01:18:51</t>
+          <t>2026-09-09 19:34:40</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,25 +753,25 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-3.95%3285</t>
+          <t>+2.89%3380</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-3.95%</t>
+          <t>+2.89%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>3285</v>
+        <v>3380</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4.32%377,000</t>
+          <t>4.45%377,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>4.32%</t>
+          <t>4.45%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-09 01:18:51</t>
+          <t>2026-09-09 19:34:40</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,25 +814,25 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-1.86%5550</t>
+          <t>+3.78%5760</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-1.86%</t>
+          <t>+3.78%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>5550</v>
+        <v>5760</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4.28%221,000</t>
+          <t>4.44%221,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4.28%</t>
+          <t>4.44%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-09 01:18:51</t>
+          <t>2026-09-09 19:34:40</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -870,38 +870,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>6669緯穎</t>
+          <t>3037欣興</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-6.02%2340</t>
+          <t>+4.09%993</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-6.02%</t>
+          <t>+4.09%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2340</v>
+        <v>993</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4.16%510,197</t>
+          <t>4.19%1,209,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4.16%</t>
+          <t>4.19%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>510197</v>
+        <v>1209000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-09 01:18:51</t>
+          <t>2026-09-09 19:34:40</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -931,38 +931,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3037欣興</t>
+          <t>6669緯穎</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+0.53%954</t>
+          <t>-0.64%2325</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+0.53%</t>
+          <t>-0.64%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>954</v>
+        <v>2325</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.02%1,209,000</t>
+          <t>4.14%510,197</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.02%</t>
+          <t>4.14%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>1209000</v>
+        <v>510197</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-09 01:18:51</t>
+          <t>2026-09-09 19:34:40</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,25 +997,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+0.42%5960</t>
+          <t>-0.59%5925</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+0.42%</t>
+          <t>-0.59%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5960</v>
+        <v>5925</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.95%190,000</t>
+          <t>3.93%190,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3.95%</t>
+          <t>3.93%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-09 01:18:51</t>
+          <t>2026-09-09 19:34:40</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,25 +1058,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+1.57%2265</t>
+          <t>+3.09%2335</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+1.57%</t>
+          <t>+3.09%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>2265</v>
+        <v>2335</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.71%470,000</t>
+          <t>3.83%470,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.71%</t>
+          <t>3.83%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-09 01:18:51</t>
+          <t>2026-09-09 19:34:40</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,25 +1119,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-2.82%5340</t>
+          <t>+0.66%5375</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-2.82%</t>
+          <t>+0.66%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5340</v>
+        <v>5375</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.26%175,000</t>
+          <t>3.28%175,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.26%</t>
+          <t>3.28%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-09 01:18:51</t>
+          <t>2026-09-09 19:34:40</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,34 +1175,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>5274信 驊</t>
+          <t>6488環球晶</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+0.03%19220</t>
+          <t>0%955</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>19220</v>
+        <v>955</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.18%47,400</t>
+          <t>3.13%938,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.18%</t>
+          <t>3.13%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>47400</v>
+        <v>938000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-09 01:18:51</t>
+          <t>2026-09-09 19:34:40</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,38 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>6488環球晶</t>
+          <t>5274信 驊</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-1.65%955</t>
+          <t>-3.2%18605</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-1.65%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>955</v>
+        <v>18605</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3.12%938,000</t>
+          <t>3.08%47,400</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3.12%</t>
+          <t>3.08%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>938000</v>
+        <v>47400</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-09 01:18:51</t>
+          <t>2026-09-09 19:34:40</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>6187萬 潤</t>
+          <t>2308台達電</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+1.09%1385</t>
+          <t>-0.55%1795</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+1.09%</t>
+          <t>-0.55%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1385</v>
+        <v>1795</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.88%596,000</t>
+          <t>2.79%446,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.88%</t>
+          <t>2.79%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>596000</v>
+        <v>446000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-09 01:18:51</t>
+          <t>2026-09-09 19:34:40</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2308台達電</t>
+          <t>6187萬 潤</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-2.43%1805</t>
+          <t>-3.97%1330</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-2.43%</t>
+          <t>-3.97%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>1805</v>
+        <v>1330</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.81%446,000</t>
+          <t>2.77%596,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.81%</t>
+          <t>2.77%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>446000</v>
+        <v>596000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-09 01:18:52</t>
+          <t>2026-09-09 19:34:41</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,12 +1424,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-1.82%1345</t>
+          <t>0%1345</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-1.82%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-09 01:18:52</t>
+          <t>2026-09-09 19:34:41</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1485,25 +1485,25 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-1.83%484</t>
+          <t>+5.17%509</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-1.83%</t>
+          <t>+5.17%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>484</v>
+        <v>509</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.74%1,034,000</t>
+          <t>1.84%1,034,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.74%</t>
+          <t>1.84%</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-09 01:18:52</t>
+          <t>2026-09-09 19:34:41</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1546,25 +1546,25 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-6.52%1935</t>
+          <t>+2.07%1975</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-6.52%</t>
+          <t>+2.07%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1935</v>
+        <v>1975</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.63%241,000</t>
+          <t>1.66%241,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.63%</t>
+          <t>1.66%</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-09 01:18:52</t>
+          <t>2026-09-09 19:34:41</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,38 +1602,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2881富邦金</t>
+          <t>2345智邦</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-0.33%149</t>
+          <t>+3.07%2015</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-0.33%</t>
+          <t>+3.07%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>149</v>
+        <v>2015</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.61%3,104,000</t>
+          <t>1.60%227,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.61%</t>
+          <t>1.60%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>3104000</v>
+        <v>227000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-09 01:18:52</t>
+          <t>2026-09-09 19:34:41</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2345智邦</t>
+          <t>2881富邦金</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-6.9%1955</t>
+          <t>-1.34%147</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-6.9%</t>
+          <t>-1.34%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1955</v>
+        <v>147</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.55%227,000</t>
+          <t>1.59%3,104,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.55%</t>
+          <t>1.59%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>227000</v>
+        <v>3104000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-09 01:18:52</t>
+          <t>2026-09-09 19:34:41</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,25 +1724,25 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2885元大金</t>
+          <t>1303南亞</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+0.57%70.6</t>
+          <t>+0.64%236.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+0.57%</t>
+          <t>+0.64%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>70.59999999999999</v>
+        <v>236.5</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.54%6,267,040</t>
+          <t>1.54%1,861,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1751,7 +1751,7 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>6267040</v>
+        <v>1861000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-09 01:18:52</t>
+          <t>2026-09-09 19:34:41</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1785,25 +1785,25 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1303南亞</t>
+          <t>2885元大金</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+1.95%235</t>
+          <t>-1.27%69.7</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+1.95%</t>
+          <t>-1.27%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>235</v>
+        <v>69.7</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.52%1,861,000</t>
+          <t>1.52%6,267,040</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1812,11 +1812,11 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>1861000</v>
+        <v>6267040</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-09 01:18:52</t>
+          <t>2026-09-09 19:34:41</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1851,25 +1851,25 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-4.02%1075</t>
+          <t>+2.33%1100</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-4.02%</t>
+          <t>+2.33%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>1075</v>
+        <v>1100</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.42%378,000</t>
+          <t>1.45%378,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>1.45%</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-09 01:18:52</t>
+          <t>2026-09-09 19:34:41</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1912,25 +1912,25 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+9.92%2825</t>
+          <t>-1.59%2780</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+9.92%</t>
+          <t>-1.59%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>2825</v>
+        <v>2780</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.20%122,000</t>
+          <t>1.18%122,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>1.18%</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-09 01:18:52</t>
+          <t>2026-09-09 19:34:41</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1973,25 +1973,25 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-3.11%747</t>
+          <t>+1.47%758</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-3.11%</t>
+          <t>+1.47%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>747</v>
+        <v>758</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.05%404,000</t>
+          <t>1.07%404,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.05%</t>
+          <t>1.07%</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-09 01:18:52</t>
+          <t>2026-09-09 19:34:41</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,38 +2029,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>3036文曄</t>
+          <t>3711日月光投控</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-1.56%189.5</t>
+          <t>+3.56%640</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-1.56%</t>
+          <t>+3.56%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>189.5</v>
+        <v>640</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.01%1,532,000</t>
+          <t>1.04%464,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>1.04%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>1532000</v>
+        <v>464000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-09 01:18:52</t>
+          <t>2026-09-09 19:34:41</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2095,25 +2095,25 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-4.2%137</t>
+          <t>+3.28%141.5</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>+3.28%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>137</v>
+        <v>141.5</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.00%2,096,000</t>
+          <t>1.04%2,096,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>1.04%</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-09 01:18:52</t>
+          <t>2026-09-09 19:34:41</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,38 +2151,38 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>3711日月光投控</t>
+          <t>3036文曄</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-0.48%618</t>
+          <t>+1.06%191.5</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-0.48%</t>
+          <t>+1.06%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>618</v>
+        <v>191.5</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.00%464,000</t>
+          <t>1.02%1,532,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>1.02%</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>464000</v>
+        <v>1532000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-09 01:18:52</t>
+          <t>2026-09-09 19:34:41</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2212,38 +2212,38 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>7750新 代</t>
+          <t>6442光 聖</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-2.53%2315</t>
+          <t>+0.29%1700</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-2.53%</t>
+          <t>+0.29%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>2315</v>
+        <v>1700</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.98%122,000</t>
+          <t>0.97%163,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.98%</t>
+          <t>0.97%</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>122000</v>
+        <v>163000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-09 01:18:52</t>
+          <t>2026-09-09 19:34:41</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,38 +2273,38 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>6442光 聖</t>
+          <t>7750新 代</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-0.29%1695</t>
+          <t>-1.94%2270</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-0.29%</t>
+          <t>-1.94%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1695</v>
+        <v>2270</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.96%163,000</t>
+          <t>0.97%122,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.97%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>163000</v>
+        <v>122000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-09 01:18:53</t>
+          <t>2026-09-09 19:34:42</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,38 +2334,38 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2449京元電子</t>
+          <t>3008大立光</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-1.65%268.5</t>
+          <t>+5.69%6870</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-1.65%</t>
+          <t>+5.69%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>268.5</v>
+        <v>6870</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.94%999,000</t>
+          <t>0.96%40,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.96%</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>999000</v>
+        <v>40000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-09 01:18:53</t>
+          <t>2026-09-09 19:34:42</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,38 +2395,38 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>3008大立光</t>
+          <t>2449京元電子</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-2.4%6500</t>
+          <t>+0.56%270</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>+0.56%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>6500</v>
+        <v>270</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.91%40,000</t>
+          <t>0.94%999,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>0.94%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>40000</v>
+        <v>999000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-09 01:18:53</t>
+          <t>2026-09-09 19:34:42</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2461,25 +2461,25 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-3.75%231</t>
+          <t>-1.3%228</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-3.75%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.89%1,107,336</t>
+          <t>0.88%1,107,336</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>0.88%</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-09 01:18:53</t>
+          <t>2026-09-09 19:34:42</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2522,16 +2522,16 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-1.76%251.5</t>
+          <t>+0.2%252</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-1.76%</t>
+          <t>+0.2%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>251.5</v>
+        <v>252</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-09 01:18:53</t>
+          <t>2026-09-09 19:34:42</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2583,16 +2583,16 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-6.68%2865</t>
+          <t>-0.52%2850</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-6.68%</t>
+          <t>-0.52%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>2865</v>
+        <v>2850</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-09 01:18:53</t>
+          <t>2026-09-09 19:34:42</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2644,25 +2644,25 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-5.61%328</t>
+          <t>+4.27%342</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-5.61%</t>
+          <t>+4.27%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>328</v>
+        <v>342</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.76%664,000</t>
+          <t>0.79%664,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.76%</t>
+          <t>0.79%</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-09 01:18:53</t>
+          <t>2026-09-09 19:34:42</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,25 +2705,25 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-2.56%152</t>
+          <t>+3.29%157</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-2.56%</t>
+          <t>+3.29%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.72%1,351,000</t>
+          <t>0.74%1,351,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.72%</t>
+          <t>0.74%</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-09 01:18:53</t>
+          <t>2026-09-09 19:34:42</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2766,16 +2766,16 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+2.54%605</t>
+          <t>+0.83%610</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+2.54%</t>
+          <t>+0.83%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-09 01:18:53</t>
+          <t>2026-09-09 19:34:42</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2822,38 +2822,38 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>6515穎崴</t>
+          <t>3374精 材</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+10%7700</t>
+          <t>+0.74%478.5</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+10%</t>
+          <t>+0.74%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>7700</v>
+        <v>478.5</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.56%21,000</t>
+          <t>0.57%340,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.56%</t>
+          <t>0.57%</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>21000</v>
+        <v>340000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-09 01:18:53</t>
+          <t>2026-09-09 19:34:42</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2883,38 +2883,38 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>3374精 材</t>
+          <t>6515穎崴</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+1.17%475</t>
+          <t>-5.45%7280</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+1.17%</t>
+          <t>-5.45%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>475</v>
+        <v>7280</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.56%340,000</t>
+          <t>0.53%21,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.56%</t>
+          <t>0.53%</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>340000</v>
+        <v>21000</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-09 01:18:53</t>
+          <t>2026-09-09 19:34:42</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,25 +2949,25 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>+6.17%6970</t>
+          <t>-3.59%6720</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>+6.17%</t>
+          <t>-3.59%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>6970</v>
+        <v>6720</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.49%20,000</t>
+          <t>0.47%20,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.47%</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-09 01:18:53</t>
+          <t>2026-09-09 19:34:42</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3005,38 +3005,38 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>3167大 量</t>
+          <t>5434崇越</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>+6.23%938</t>
+          <t>+0.56%535</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+6.23%</t>
+          <t>+0.56%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>938</v>
+        <v>535</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.38%115,000</t>
+          <t>0.37%200,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.37%</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>115000</v>
+        <v>200000</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-09 01:18:53</t>
+          <t>2026-09-09 19:34:42</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3066,38 +3066,38 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>5434崇越</t>
+          <t>3167大 量</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-1.66%532</t>
+          <t>-4.05%900</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-1.66%</t>
+          <t>-4.05%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>532</v>
+        <v>900</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.37%200,000</t>
+          <t>0.36%115,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.36%</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>200000</v>
+        <v>115000</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-09 01:18:53</t>
+          <t>2026-09-09 19:34:42</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3132,25 +3132,25 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-2.33%167.5</t>
+          <t>-0.9%166</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-2.33%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>167.5</v>
+        <v>166</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.35%592,000</t>
+          <t>0.34%592,000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.34%</t>
         </is>
       </c>
       <c r="K45" t="n">
@@ -3158,7 +3158,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-09 01:18:53</t>
+          <t>2026-09-09 19:34:42</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3193,12 +3193,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-0.28%708</t>
+          <t>0%708</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H46" t="n">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">

--- a/etf_holdings/2026-09-09_00400A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-09_00400A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:40</t>
+          <t>2026-09-09 22:38:07</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:40</t>
+          <t>2026-09-09 22:38:07</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:40</t>
+          <t>2026-09-09 22:38:07</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:40</t>
+          <t>2026-09-09 22:38:07</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:40</t>
+          <t>2026-09-09 22:38:07</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:40</t>
+          <t>2026-09-09 22:38:07</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:40</t>
+          <t>2026-09-09 22:38:07</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:40</t>
+          <t>2026-09-09 22:38:07</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:40</t>
+          <t>2026-09-09 22:38:07</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:40</t>
+          <t>2026-09-09 22:38:07</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:40</t>
+          <t>2026-09-09 22:38:07</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:40</t>
+          <t>2026-09-09 22:38:07</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:40</t>
+          <t>2026-09-09 22:38:07</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:40</t>
+          <t>2026-09-09 22:38:07</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:40</t>
+          <t>2026-09-09 22:38:07</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:41</t>
+          <t>2026-09-09 22:38:09</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:41</t>
+          <t>2026-09-09 22:38:09</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:41</t>
+          <t>2026-09-09 22:38:09</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:41</t>
+          <t>2026-09-09 22:38:09</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:41</t>
+          <t>2026-09-09 22:38:09</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:41</t>
+          <t>2026-09-09 22:38:09</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:41</t>
+          <t>2026-09-09 22:38:09</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:41</t>
+          <t>2026-09-09 22:38:09</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:41</t>
+          <t>2026-09-09 22:38:09</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:41</t>
+          <t>2026-09-09 22:38:09</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:41</t>
+          <t>2026-09-09 22:38:09</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:41</t>
+          <t>2026-09-09 22:38:09</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:41</t>
+          <t>2026-09-09 22:38:09</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:41</t>
+          <t>2026-09-09 22:38:09</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:41</t>
+          <t>2026-09-09 22:38:09</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:42</t>
+          <t>2026-09-09 22:38:10</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:42</t>
+          <t>2026-09-09 22:38:10</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:42</t>
+          <t>2026-09-09 22:38:10</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:42</t>
+          <t>2026-09-09 22:38:10</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:42</t>
+          <t>2026-09-09 22:38:10</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:42</t>
+          <t>2026-09-09 22:38:10</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:42</t>
+          <t>2026-09-09 22:38:10</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:42</t>
+          <t>2026-09-09 22:38:10</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:42</t>
+          <t>2026-09-09 22:38:10</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:42</t>
+          <t>2026-09-09 22:38:10</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:42</t>
+          <t>2026-09-09 22:38:10</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:42</t>
+          <t>2026-09-09 22:38:10</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:42</t>
+          <t>2026-09-09 22:38:10</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:42</t>
+          <t>2026-09-09 22:38:10</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-09 19:34:42</t>
+          <t>2026-09-09 22:38:10</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">

--- a/etf_holdings/2026-09-09_00400A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-09_00400A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 22:38:07</t>
+          <t>2026-09-09 22:49:57</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09 22:38:07</t>
+          <t>2026-09-09 22:49:57</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09 22:38:07</t>
+          <t>2026-09-09 22:49:57</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-09 22:38:07</t>
+          <t>2026-09-09 22:49:57</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-09 22:38:07</t>
+          <t>2026-09-09 22:49:57</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-09 22:38:07</t>
+          <t>2026-09-09 22:49:57</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-09 22:38:07</t>
+          <t>2026-09-09 22:49:57</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-09 22:38:07</t>
+          <t>2026-09-09 22:49:57</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-09 22:38:07</t>
+          <t>2026-09-09 22:49:57</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-09 22:38:07</t>
+          <t>2026-09-09 22:49:57</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-09 22:38:07</t>
+          <t>2026-09-09 22:49:57</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-09 22:38:07</t>
+          <t>2026-09-09 22:49:57</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-09 22:38:07</t>
+          <t>2026-09-09 22:49:57</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-09 22:38:07</t>
+          <t>2026-09-09 22:49:57</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-09 22:38:07</t>
+          <t>2026-09-09 22:49:57</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-09 22:38:09</t>
+          <t>2026-09-09 22:49:59</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-09 22:38:09</t>
+          <t>2026-09-09 22:49:59</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-09 22:38:09</t>
+          <t>2026-09-09 22:49:59</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-09 22:38:09</t>
+          <t>2026-09-09 22:49:59</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-09 22:38:09</t>
+          <t>2026-09-09 22:49:59</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-09 22:38:09</t>
+          <t>2026-09-09 22:49:59</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-09 22:38:09</t>
+          <t>2026-09-09 22:49:59</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-09 22:38:09</t>
+          <t>2026-09-09 22:49:59</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-09 22:38:09</t>
+          <t>2026-09-09 22:49:59</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-09 22:38:09</t>
+          <t>2026-09-09 22:49:59</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-09 22:38:09</t>
+          <t>2026-09-09 22:49:59</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-09 22:38:09</t>
+          <t>2026-09-09 22:49:59</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-09 22:38:09</t>
+          <t>2026-09-09 22:49:59</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-09 22:38:09</t>
+          <t>2026-09-09 22:49:59</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-09 22:38:09</t>
+          <t>2026-09-09 22:49:59</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-09 22:38:10</t>
+          <t>2026-09-09 22:50:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-09 22:38:10</t>
+          <t>2026-09-09 22:50:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-09 22:38:10</t>
+          <t>2026-09-09 22:50:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-09 22:38:10</t>
+          <t>2026-09-09 22:50:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-09 22:38:10</t>
+          <t>2026-09-09 22:50:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-09 22:38:10</t>
+          <t>2026-09-09 22:50:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-09 22:38:10</t>
+          <t>2026-09-09 22:50:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-09 22:38:10</t>
+          <t>2026-09-09 22:50:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-09 22:38:10</t>
+          <t>2026-09-09 22:50:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-09 22:38:10</t>
+          <t>2026-09-09 22:50:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-09 22:38:10</t>
+          <t>2026-09-09 22:50:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-09 22:38:10</t>
+          <t>2026-09-09 22:50:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-09 22:38:10</t>
+          <t>2026-09-09 22:50:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-09 22:38:10</t>
+          <t>2026-09-09 22:50:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-09 22:38:10</t>
+          <t>2026-09-09 22:50:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">

--- a/etf_holdings/2026-09-09_00400A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-09_00400A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:57</t>
+          <t>2026-09-09 23:10:55</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:57</t>
+          <t>2026-09-09 23:10:55</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:57</t>
+          <t>2026-09-09 23:10:55</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:57</t>
+          <t>2026-09-09 23:10:55</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:57</t>
+          <t>2026-09-09 23:10:55</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:57</t>
+          <t>2026-09-09 23:10:55</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:57</t>
+          <t>2026-09-09 23:10:55</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:57</t>
+          <t>2026-09-09 23:10:55</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:57</t>
+          <t>2026-09-09 23:10:55</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:57</t>
+          <t>2026-09-09 23:10:55</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:57</t>
+          <t>2026-09-09 23:10:55</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:57</t>
+          <t>2026-09-09 23:10:55</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:57</t>
+          <t>2026-09-09 23:10:55</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:57</t>
+          <t>2026-09-09 23:10:55</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:57</t>
+          <t>2026-09-09 23:10:55</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:59</t>
+          <t>2026-09-09 23:10:57</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:59</t>
+          <t>2026-09-09 23:10:57</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:59</t>
+          <t>2026-09-09 23:10:57</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:59</t>
+          <t>2026-09-09 23:10:57</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:59</t>
+          <t>2026-09-09 23:10:57</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:59</t>
+          <t>2026-09-09 23:10:57</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:59</t>
+          <t>2026-09-09 23:10:57</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:59</t>
+          <t>2026-09-09 23:10:57</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:59</t>
+          <t>2026-09-09 23:10:57</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:59</t>
+          <t>2026-09-09 23:10:57</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:59</t>
+          <t>2026-09-09 23:10:57</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:59</t>
+          <t>2026-09-09 23:10:57</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:59</t>
+          <t>2026-09-09 23:10:57</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:59</t>
+          <t>2026-09-09 23:10:57</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:59</t>
+          <t>2026-09-09 23:10:57</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-09 22:50:00</t>
+          <t>2026-09-09 23:10:58</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-09 22:50:00</t>
+          <t>2026-09-09 23:10:58</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-09 22:50:00</t>
+          <t>2026-09-09 23:10:58</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-09 22:50:00</t>
+          <t>2026-09-09 23:10:58</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-09 22:50:00</t>
+          <t>2026-09-09 23:10:58</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-09 22:50:00</t>
+          <t>2026-09-09 23:10:58</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-09 22:50:00</t>
+          <t>2026-09-09 23:10:58</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-09 22:50:00</t>
+          <t>2026-09-09 23:10:58</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-09 22:50:00</t>
+          <t>2026-09-09 23:10:58</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-09 22:50:00</t>
+          <t>2026-09-09 23:10:58</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-09 22:50:00</t>
+          <t>2026-09-09 23:10:58</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-09 22:50:00</t>
+          <t>2026-09-09 23:10:58</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-09 22:50:00</t>
+          <t>2026-09-09 23:10:58</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-09 22:50:00</t>
+          <t>2026-09-09 23:10:58</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-09 22:50:00</t>
+          <t>2026-09-09 23:10:58</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
